--- a/data/industry_sectors_unconstrained.xlsx
+++ b/data/industry_sectors_unconstrained.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9B07E2F-5AE8-4582-85A2-A44BF6A95EB9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F6FEF7-ADBD-4701-9E00-55D7A90DEAC2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
-    <sheet name="Dates &amp; Risk Free Rate" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Ticker</t>
   </si>
@@ -43,15 +42,6 @@
   </si>
   <si>
     <t>Max Weight</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Risk Free Rate</t>
   </si>
   <si>
     <t>XLC</t>
@@ -149,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -168,14 +158,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -510,176 +492,134 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="11">
+        <v>14</v>
+      </c>
+      <c r="B2" s="7">
         <v>0</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C3" s="12">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C4" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C4" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C5" s="12">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C5" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C6" s="12">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C6" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C7" s="12">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C8" s="12">
+        <v>8</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C9" s="12">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C10" s="12">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C10" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C11" s="12">
+        <v>11</v>
+      </c>
+      <c r="B11" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C11" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C12" s="12">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C12" s="8">
         <v>0.99999000000000005</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="11">
-        <v>0.03</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0.99999000000000005</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{127E0FCD-DF27-4C1E-9060-A66EB07DD960}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="3" width="13.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
-        <f ca="1">DATE(YEAR(B2)-10,MONTH(B2),DAY(B2))</f>
-        <v>41863</v>
-      </c>
-      <c r="B2" s="9">
-        <f ca="1">NOW()-1</f>
-        <v>45516.664201273146</v>
-      </c>
-      <c r="C2" s="10">
-        <v>5.1499999999999997E-2</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.99999000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry_sectors_unconstrained.xlsx
+++ b/data/industry_sectors_unconstrained.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F6FEF7-ADBD-4701-9E00-55D7A90DEAC2}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B138F9B-CBE9-4A56-856F-FB15B695E08E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,7 +506,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C3" s="8">
         <v>0.99999000000000005</v>
@@ -517,7 +517,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C4" s="8">
         <v>0.99999000000000005</v>
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C5" s="8">
         <v>0.99999000000000005</v>
@@ -539,7 +539,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C6" s="8">
         <v>0.99999000000000005</v>
@@ -550,7 +550,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8">
         <v>0.99999000000000005</v>
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C8" s="8">
         <v>0.99999000000000005</v>
@@ -572,7 +572,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C9" s="8">
         <v>0.99999000000000005</v>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C10" s="8">
         <v>0.99999000000000005</v>
@@ -594,7 +594,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C11" s="8">
         <v>0.99999000000000005</v>
@@ -605,7 +605,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C12" s="8">
         <v>0.99999000000000005</v>
@@ -616,7 +616,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="7">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C13" s="8">
         <v>0.99999000000000005</v>

--- a/data/industry_sectors_unconstrained.xlsx
+++ b/data/industry_sectors_unconstrained.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B138F9B-CBE9-4A56-856F-FB15B695E08E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{95059BB6-7B32-43CC-A2D9-70D951C7B34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AEC742D-B576-4E19-A449-27F196BD135F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40" yWindow="0" windowWidth="25560" windowHeight="13660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Ticker</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>BIL</t>
+  </si>
+  <si>
+    <t>Curr Weight</t>
   </si>
 </sst>
 </file>
@@ -471,15 +474,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +493,11 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -501,7 +508,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -512,7 +519,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -523,7 +530,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -534,7 +541,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -545,7 +552,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -556,7 +563,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -567,7 +574,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
@@ -578,7 +585,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -589,7 +596,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -600,7 +607,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -611,7 +618,7 @@
         <v>0.99999000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
